--- a/artfynd/A 22248-2026 artfynd.xlsx
+++ b/artfynd/A 22248-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132914310</v>
       </c>
       <c r="B2" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22248-2026 artfynd.xlsx
+++ b/artfynd/A 22248-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132914310</v>
       </c>
       <c r="B2" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22248-2026 artfynd.xlsx
+++ b/artfynd/A 22248-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132914310</v>
+        <v>133132385</v>
       </c>
       <c r="B2" t="n">
-        <v>98005</v>
+        <v>57162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,16 +708,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lilla Orrmossen, Lilla Orrmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483875</v>
+        <v>484044</v>
       </c>
       <c r="R2" t="n">
-        <v>6596624</v>
+        <v>6596585</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,17 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,15 +789,459 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133133945</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kröket, Kröket, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>484266</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6596504</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132914310</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483875</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6596624</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132914311</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>484004</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6596753</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134232493</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484015</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6596402</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22248-2026 artfynd.xlsx
+++ b/artfynd/A 22248-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133132385</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133133945</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132914310</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132914311</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,8 +1267,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232493</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>